--- a/test-cases/SauceDemo_Manual_Test_Cases.xlsx
+++ b/test-cases/SauceDemo_Manual_Test_Cases.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <fileSharing readOnlyRecommended="1"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dewmie Wijewardhana\Desktop\Test cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DFF690-E924-4FB8-82E0-07762C1E3E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57C034C-BF2F-49E5-8797-A84FF318F995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="240" windowWidth="14952" windowHeight="11556" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plan" sheetId="1" r:id="rId1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="342">
   <si>
     <t>Project</t>
   </si>
@@ -1193,6 +1192,9 @@
   </si>
   <si>
     <t>Manual Testing Project - Sauce Demo Web Application</t>
+  </si>
+  <si>
+    <t>Priority</t>
   </si>
 </sst>
 </file>
@@ -1822,13 +1824,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>387592</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>156081</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>2645276</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>1169541</xdr:rowOff>
@@ -1866,13 +1868,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>128427</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>154112</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>3445398</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>402404</xdr:rowOff>
@@ -1910,13 +1912,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>102741</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>530832</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>2688404</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>1752064</xdr:rowOff>
@@ -1954,13 +1956,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>152402</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>254001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>3563258</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>515823</xdr:rowOff>
@@ -3578,21 +3580,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="2" customWidth="1"/>
     <col min="2" max="2" width="38" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="14" style="2" customWidth="1"/>
     <col min="5" max="5" width="48" style="2" customWidth="1"/>
     <col min="6" max="7" width="38" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12" style="2" customWidth="1"/>
-    <col min="9" max="9" width="52.33203125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="2"/>
+    <col min="8" max="9" width="12" style="2" customWidth="1"/>
+    <col min="10" max="10" width="52.33203125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>199</v>
       </c>
@@ -3618,10 +3620,13 @@
         <v>203</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>207</v>
       </c>
@@ -3646,8 +3651,11 @@
       <c r="H2" s="16" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>215</v>
       </c>
@@ -3672,8 +3680,11 @@
       <c r="H3" s="16" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>220</v>
       </c>
@@ -3698,8 +3709,11 @@
       <c r="H4" s="16" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>225</v>
       </c>
@@ -3724,8 +3738,11 @@
       <c r="H5" s="17" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>229</v>
       </c>
@@ -3750,8 +3767,11 @@
       <c r="H6" s="18" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>237</v>
       </c>
@@ -3776,8 +3796,11 @@
       <c r="H7" s="18" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>242</v>
       </c>
@@ -3802,8 +3825,11 @@
       <c r="H8" s="16" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="149.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>247</v>
       </c>
@@ -3828,8 +3854,11 @@
       <c r="H9" s="19" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="19" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>319</v>
       </c>
@@ -3854,10 +3883,13 @@
       <c r="H10" s="19" t="s">
         <v>250</v>
       </c>
+      <c r="I10" s="19" t="s">
+        <v>233</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:I10">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Low"</formula>
     </cfRule>
@@ -3872,7 +3904,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Severity" error="Please select a severity level from the dropdown list: Critical, High, Medium, or Low." sqref="H2:H10" xr:uid="{9FA62390-9DE3-449D-8A8B-3D1341220F5D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Severity" error="Please select a severity level from the dropdown list: Critical, High, Medium, or Low." sqref="H2:I10" xr:uid="{9FA62390-9DE3-449D-8A8B-3D1341220F5D}">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
